--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N7_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N7_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>37.77238259322372</v>
+        <v>6.138012171398856</v>
       </c>
       <c r="D2" t="n">
-        <v>37.81999565551779</v>
+        <v>6.145749294021642</v>
       </c>
       <c r="E2" t="n">
-        <v>4.700076968897888</v>
+        <v>0.7637625074459069</v>
       </c>
       <c r="F2" t="n">
-        <v>9.240673184118597</v>
+        <v>1.501609392419272</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>36.36945363691189</v>
+        <v>5.910036215998182</v>
       </c>
       <c r="D3" t="n">
-        <v>36.23579130645169</v>
+        <v>5.888316087298399</v>
       </c>
       <c r="E3" t="n">
-        <v>4.700076968897888</v>
+        <v>0.7637625074459069</v>
       </c>
       <c r="F3" t="n">
-        <v>9.240673184118597</v>
+        <v>1.501609392419272</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>47.59869115943697</v>
+        <v>7.734787313408509</v>
       </c>
       <c r="D4" t="n">
-        <v>15.52938802274935</v>
+        <v>2.52352555369677</v>
       </c>
       <c r="E4" t="n">
-        <v>4.700076968897888</v>
+        <v>0.7637625074459069</v>
       </c>
       <c r="F4" t="n">
-        <v>9.240673184118597</v>
+        <v>1.501609392419272</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>36.33919283234175</v>
+        <v>5.905118835255535</v>
       </c>
       <c r="D5" t="n">
-        <v>36.41219441806161</v>
+        <v>5.916981592935012</v>
       </c>
       <c r="E5" t="n">
-        <v>4.700076968897888</v>
+        <v>0.7637625074459069</v>
       </c>
       <c r="F5" t="n">
-        <v>9.240673184118597</v>
+        <v>1.501609392419272</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
